--- a/docs/BandiRadar.xlsx
+++ b/docs/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -619,14 +619,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 19/06/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 14 bandi verificati + 3 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 14 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>11gg</t>
+          <t>8gg</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>42gg</t>
+          <t>39gg</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>42gg</t>
+          <t>39gg</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>103gg</t>
+          <t>100gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>168gg</t>
+          <t>165gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>376gg</t>
+          <t>373gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>560gg</t>
+          <t>557gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>195gg</t>
+          <t>192gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1738,18 +1738,80 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17 bandi | 16 aperti | 1 in scadenza | 14 verificati manualmente | Aggiornato: 19/06/2026</t>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Interventi speciali a favore della montagna di cui alla DGR 7391/2022</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Digitalizzazione / Transizione 4.0</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>192gg</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  18 bandi | 17 aperti | 1 in scadenza | 14 verificati manualmente | Aggiornato: 22/06/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L20"/>
+  <autoFilter ref="A3:L21"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
@@ -1770,6 +1832,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1794,7 +1857,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 19/06/2026</t>
+          <t>DASHBOARD — 22/06/2026</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1913,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>11 gg</t>
+          <t>8 gg</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">

--- a/docs/BandiRadar.xlsx
+++ b/docs/BandiRadar.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info &amp; Fonti" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bandi Attivi'!$A$3:$L$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -619,14 +619,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 22/06/2026</t>
+          <t>BANDIRADAR — Monitor Bandi &amp; Contributi per PMI | Aggiornato: 29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dataset: 14 bandi verificati + 4 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
+          <t>Dataset: 14 bandi verificati + 5 trovati automaticamente | Link pubblico: github.com/TUO-USERNAME/bandi-radar</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>8gg</t>
+          <t>1gg</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>39gg</t>
+          <t>32gg</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>39gg</t>
+          <t>32gg</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>100gg</t>
+          <t>93gg</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>165gg</t>
+          <t>158gg</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>373gg</t>
+          <t>366gg</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>557gg</t>
+          <t>550gg</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Attività Produttive/Imprese</t>
+          <t>Contributo integrativo Regionale sulla spesa assicurativa agevolata “Sma...</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>31/12/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>93gg</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Istruzione, Formazione e Lavoro</t>
+          <t>Attività Produttive/Imprese</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ricerca e Innovazione</t>
+          <t>Istruzione, Formazione e Lavoro</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>192gg</t>
+          <t>185gg</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1741,78 +1741,140 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Ricerca e Innovazione</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia Bandi</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Regione Lombardia</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Vedere bando</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>185gg</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Apri</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Interventi speciali a favore della montagna di cui alla DGR 7391/2022</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Regione Lombardia Bandi</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Regione Lombardia</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Digitalizzazione / Transizione 4.0</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Vedere bando</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Vedere bando</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>31/12/2026</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>192gg</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>185gg</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Trovato automaticamente su Regione Lombardia Bandi — verificare prima dell'uso</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Apri</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18 bandi | 17 aperti | 1 in scadenza | 14 verificati manualmente | Aggiornato: 22/06/2026</t>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  19 bandi | 18 aperti | 1 in scadenza | 14 verificati manualmente | Aggiornato: 29/06/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L21"/>
+  <autoFilter ref="A3:L22"/>
   <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A23:L23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId1"/>
@@ -1833,6 +1895,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1857,7 +1920,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DASHBOARD — 22/06/2026</t>
+          <t>DASHBOARD — 29/06/2026</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1976,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>8 gg</t>
+          <t>1 gg</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
